--- a/data/trans_dic/P6902-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P6902-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que se siente nervioso y estresado</t>
+          <t>Población que su trabajo le afecta de manera que se siente nervioso y estresado (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,94; 35,37</t>
+          <t>18,74; 34,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23,03; 46,61</t>
+          <t>22,23; 47,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27,96; 56,77</t>
+          <t>28,37; 56,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32,6; 68,58</t>
+          <t>30,6; 69,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,59; 42,02</t>
+          <t>13,75; 43,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,95; 67,3</t>
+          <t>35,16; 66,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,47; 50,05</t>
+          <t>10,83; 54,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20,12; 65,84</t>
+          <t>21,72; 66,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,36; 34,5</t>
+          <t>19,42; 33,61</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31,32; 52,49</t>
+          <t>30,6; 52,1</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26,83; 50,23</t>
+          <t>28,71; 50,29</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>31,57; 62,55</t>
+          <t>31,97; 61,71</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>35,21; 47,02</t>
+          <t>35,71; 47,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37,84; 52,21</t>
+          <t>37,94; 52,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,11; 42,7</t>
+          <t>29,82; 42,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48,03; 62,36</t>
+          <t>48,61; 62,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>40,27; 58,93</t>
+          <t>39,74; 59,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,06; 62,67</t>
+          <t>45,33; 63,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,16; 67,04</t>
+          <t>50,41; 68,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>30,88; 61,96</t>
+          <t>32,76; 62,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>38,81; 48,76</t>
+          <t>38,77; 48,72</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43,29; 54,26</t>
+          <t>43,03; 53,95</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38,95; 49,77</t>
+          <t>38,86; 49,66</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>41,03; 59,95</t>
+          <t>42,22; 59,81</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>65,81; 86,04</t>
+          <t>66,79; 86,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>56,57; 83,49</t>
+          <t>56,34; 83,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>55,92; 79,33</t>
+          <t>55,15; 80,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>75,18; 93,38</t>
+          <t>75,93; 93,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>56,84; 79,78</t>
+          <t>56,74; 80,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>56,47; 84,95</t>
+          <t>55,26; 85,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60,13; 82,4</t>
+          <t>59,82; 81,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>81,59; 92,45</t>
+          <t>81,81; 92,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>65,53; 80,5</t>
+          <t>65,57; 81,01</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>62,21; 80,68</t>
+          <t>61,25; 81,59</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>61,61; 77,34</t>
+          <t>60,76; 77,85</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>81,79; 91,82</t>
+          <t>81,91; 92,0</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>38,71; 48,01</t>
+          <t>39,26; 48,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41,84; 52,4</t>
+          <t>41,35; 53,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37,0; 48,87</t>
+          <t>37,86; 49,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56,23; 67,41</t>
+          <t>56,38; 67,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>45,02; 58,75</t>
+          <t>44,37; 57,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,04; 64,04</t>
+          <t>49,92; 64,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,61; 67,05</t>
+          <t>53,8; 66,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>45,01; 68,53</t>
+          <t>43,29; 68,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>42,18; 49,68</t>
+          <t>42,3; 49,9</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46,63; 55,52</t>
+          <t>46,37; 55,37</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45,16; 54,11</t>
+          <t>45,9; 54,36</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>51,37; 65,87</t>
+          <t>50,67; 65,83</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que se siente nervioso y estresado</t>
+          <t>Población que su trabajo le afecta de manera que se siente nervioso y estresado (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19963; 39358</t>
+          <t>20858; 38935</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12967; 26249</t>
+          <t>12518; 26514</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15542; 31554</t>
+          <t>15770; 31536</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9523; 20035</t>
+          <t>8941; 20438</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5106; 15786</t>
+          <t>5165; 16187</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13260; 25531</t>
+          <t>13337; 25315</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1888; 9022</t>
+          <t>1953; 9845</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5027; 16451</t>
+          <t>5426; 16680</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>28818; 51351</t>
+          <t>28901; 50035</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29524; 49477</t>
+          <t>28844; 49102</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19745; 36968</t>
+          <t>21133; 37014</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17110; 33901</t>
+          <t>17329; 33446</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>101022; 134913</t>
+          <t>102465; 136272</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>83903; 115774</t>
+          <t>84126; 116061</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69067; 97948</t>
+          <t>68392; 97828</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>115066; 149398</t>
+          <t>116453; 148812</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>47749; 69874</t>
+          <t>47117; 69993</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>59287; 82461</t>
+          <t>59644; 83416</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>62481; 83505</t>
+          <t>62791; 84944</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>73607; 147688</t>
+          <t>78079; 148864</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>157397; 197733</t>
+          <t>157230; 197565</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>152931; 191698</t>
+          <t>152027; 190613</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>137879; 176167</t>
+          <t>137554; 175758</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>196091; 286539</t>
+          <t>201767; 285854</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>48748; 63735</t>
+          <t>49476; 63904</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>26074; 38479</t>
+          <t>25965; 38677</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35525; 50397</t>
+          <t>35033; 51085</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52266; 64924</t>
+          <t>52793; 65331</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>36371; 51046</t>
+          <t>36303; 51195</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26158; 39347</t>
+          <t>25598; 39685</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>44322; 60734</t>
+          <t>44089; 60378</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>73995; 83848</t>
+          <t>74195; 84037</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>90475; 111137</t>
+          <t>90523; 111842</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>57492; 74556</t>
+          <t>56603; 75399</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>84546; 106142</t>
+          <t>83389; 106833</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>131052; 147118</t>
+          <t>131230; 147397</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>182842; 226766</t>
+          <t>185412; 229307</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>135610; 169862</t>
+          <t>134023; 172898</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>128939; 170316</t>
+          <t>131952; 170988</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>190246; 228055</t>
+          <t>190730; 227200</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>99095; 129325</t>
+          <t>97668; 126680</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>108010; 138217</t>
+          <t>107731; 138490</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>115947; 145027</t>
+          <t>116377; 144767</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>159343; 242634</t>
+          <t>153253; 243025</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>292085; 343979</t>
+          <t>292908; 345489</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>251774; 299801</t>
+          <t>250406; 298969</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>255048; 305583</t>
+          <t>259253; 307027</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>355661; 456039</t>
+          <t>350800; 455802</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P6902-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P6902-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>50,23%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,74; 34,99</t>
+          <t>18,48; 35,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,23; 47,08</t>
+          <t>22,33; 47,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28,37; 56,74</t>
+          <t>28,29; 57,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30,6; 69,96</t>
+          <t>32,24; 67,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,75; 43,09</t>
+          <t>13,53; 42,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,16; 66,73</t>
+          <t>32,37; 66,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,83; 54,62</t>
+          <t>10,59; 50,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,72; 66,76</t>
+          <t>34,44; 67,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,42; 33,61</t>
+          <t>19,95; 34,0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30,6; 52,1</t>
+          <t>31,63; 51,67</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,71; 50,29</t>
+          <t>27,13; 50,51</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>31,97; 61,71</t>
+          <t>37,49; 62,66</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>57,74%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>35,71; 47,49</t>
+          <t>35,4; 47,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37,94; 52,34</t>
+          <t>38,61; 52,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29,82; 42,65</t>
+          <t>29,87; 43,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48,61; 62,11</t>
+          <t>49,31; 61,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>39,74; 59,03</t>
+          <t>39,75; 58,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,33; 63,4</t>
+          <t>45,2; 62,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,41; 68,19</t>
+          <t>49,41; 67,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>32,76; 62,45</t>
+          <t>54,89; 65,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>38,77; 48,72</t>
+          <t>38,1; 48,03</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43,03; 53,95</t>
+          <t>42,63; 54,32</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38,86; 49,66</t>
+          <t>38,9; 49,47</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>42,22; 59,81</t>
+          <t>53,05; 62,21</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,42%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>66,79; 86,27</t>
+          <t>65,9; 86,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>56,34; 83,92</t>
+          <t>57,9; 82,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>55,15; 80,41</t>
+          <t>55,15; 78,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>75,93; 93,97</t>
+          <t>76,61; 94,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>56,74; 80,01</t>
+          <t>56,39; 80,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>55,26; 85,67</t>
+          <t>55,6; 84,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>59,82; 81,92</t>
+          <t>60,37; 81,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>81,81; 92,66</t>
+          <t>80,16; 91,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>65,57; 81,01</t>
+          <t>65,31; 80,89</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>61,25; 81,59</t>
+          <t>61,94; 81,42</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>60,76; 77,85</t>
+          <t>61,53; 78,29</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>81,91; 92,0</t>
+          <t>81,25; 91,2</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>64,33%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,26; 48,55</t>
+          <t>38,46; 48,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41,35; 53,34</t>
+          <t>41,49; 52,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37,86; 49,07</t>
+          <t>37,71; 48,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56,38; 67,16</t>
+          <t>54,98; 66,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>44,37; 57,55</t>
+          <t>44,12; 57,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,92; 64,17</t>
+          <t>49,47; 63,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,8; 66,93</t>
+          <t>53,42; 66,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>43,29; 68,64</t>
+          <t>62,83; 71,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>42,3; 49,9</t>
+          <t>41,73; 49,52</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46,37; 55,37</t>
+          <t>46,36; 55,56</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45,9; 54,36</t>
+          <t>45,67; 54,17</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>50,67; 65,83</t>
+          <t>60,8; 67,87</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14718</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11354</t>
+          <t>12802</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26072</t>
+          <t>30503</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20858; 38935</t>
+          <t>20567; 39353</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12518; 26514</t>
+          <t>12574; 26645</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15770; 31536</t>
+          <t>15725; 31749</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8941; 20438</t>
+          <t>11676; 24520</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5165; 16187</t>
+          <t>5083; 16114</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13337; 25315</t>
+          <t>12278; 25360</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1953; 9845</t>
+          <t>1908; 9083</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5426; 16680</t>
+          <t>8439; 16511</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>28901; 50035</t>
+          <t>29689; 50612</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>28844; 49102</t>
+          <t>29809; 48704</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21133; 37014</t>
+          <t>19966; 37179</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17329; 33446</t>
+          <t>22765; 38047</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>133548</t>
+          <t>149812</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>123394</t>
+          <t>133458</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>256941</t>
+          <t>283270</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>102465; 136272</t>
+          <t>101574; 137230</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>84126; 116061</t>
+          <t>85605; 116507</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>68392; 97828</t>
+          <t>68524; 99454</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>116453; 148812</t>
+          <t>133002; 167016</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>47117; 69993</t>
+          <t>47131; 69103</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>59644; 83416</t>
+          <t>59469; 82282</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>62791; 84944</t>
+          <t>61543; 83663</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>78079; 148864</t>
+          <t>121221; 145405</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>157230; 197565</t>
+          <t>154513; 194782</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>152027; 190613</t>
+          <t>150614; 191910</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>137554; 175758</t>
+          <t>137681; 175091</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>201767; 285854</t>
+          <t>260251; 305207</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60515</t>
+          <t>68408</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>79575</t>
+          <t>86471</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>140089</t>
+          <t>154879</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>49476; 63904</t>
+          <t>48812; 63735</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>25965; 38677</t>
+          <t>26686; 38160</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35033; 51085</t>
+          <t>35038; 50086</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52793; 65331</t>
+          <t>59578; 73484</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>36303; 51195</t>
+          <t>36078; 51550</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25598; 39685</t>
+          <t>25755; 39330</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>44089; 60378</t>
+          <t>44499; 60277</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>74195; 84037</t>
+          <t>79689; 90901</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>90523; 111842</t>
+          <t>90165; 111678</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>56603; 75399</t>
+          <t>57240; 75239</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>83389; 106833</t>
+          <t>84443; 107439</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>131230; 147397</t>
+          <t>143955; 161584</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>208781</t>
+          <t>235921</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>214322</t>
+          <t>232732</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>423103</t>
+          <t>468654</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>185412; 229307</t>
+          <t>181641; 228714</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>134023; 172898</t>
+          <t>134492; 171242</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>131952; 170988</t>
+          <t>131425; 170246</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>190730; 227200</t>
+          <t>210974; 254173</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>97668; 126680</t>
+          <t>97113; 126572</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>107731; 138490</t>
+          <t>106769; 137870</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>116377; 144767</t>
+          <t>115538; 144165</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>153253; 243025</t>
+          <t>216616; 246686</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>292908; 345489</t>
+          <t>288922; 342872</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>250406; 298969</t>
+          <t>250348; 299983</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>259253; 307027</t>
+          <t>257914; 305934</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>350800; 455802</t>
+          <t>442896; 494465</t>
         </is>
       </c>
     </row>
